--- a/需求的模板/需要的数据/HScode库.xlsx
+++ b/需求的模板/需要的数据/HScode库.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="268">
   <si>
     <t>HS Code</t>
   </si>
@@ -942,6 +942,22 @@
   <si>
     <t>上海</t>
   </si>
+  <si>
+    <t>机动车辆上供人使用的空气调节器</t>
+  </si>
+  <si>
+    <t>变频驻车空调</t>
+  </si>
+  <si>
+    <t>ZKF-20GW/DB4W2A</t>
+  </si>
+  <si>
+    <t>1. 品牌类型 ：境内自主品牌
+2. 出口享惠情况：
+3. 用途：驻车空调用
+4. 品牌：海信
+5. 型号：ZKF-20GW/DB4W2A</t>
+  </si>
 </sst>
 </file>
 
@@ -953,7 +969,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -976,6 +992,11 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1123,7 +1144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1138,6 +1159,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1323,7 +1350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1343,6 +1370,34 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1464,55 +1519,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
@@ -1527,70 +1579,73 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1600,7 +1655,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1612,12 +1667,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2163,49 +2239,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H64"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
     <col min="3" max="3" width="21.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="23.625" style="3" customWidth="1"/>
-    <col min="5" max="6" width="44.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="44.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="44.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="15.125" style="2" customWidth="1"/>
-    <col min="8" max="11" width="9" style="4" customWidth="1"/>
-    <col min="12" max="12" width="29.75" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4" customWidth="1"/>
+    <col min="8" max="11" width="9" style="5" customWidth="1"/>
+    <col min="12" max="12" width="29.75" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -2214,7 +2291,7 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F2"/>
@@ -2223,7 +2300,7 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:8">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
@@ -2235,7 +2312,7 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F3"/>
@@ -2244,7 +2321,7 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
@@ -2256,7 +2333,7 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F4"/>
@@ -2265,7 +2342,7 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B5" t="s">
@@ -2277,7 +2354,7 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F5"/>
@@ -2286,7 +2363,7 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
@@ -2295,7 +2372,7 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F6"/>
@@ -2304,7 +2381,7 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B7" t="s">
@@ -2316,7 +2393,7 @@
       <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F7"/>
@@ -2325,7 +2402,7 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B8" t="s">
@@ -2337,7 +2414,7 @@
       <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="8" t="s">
         <v>37</v>
       </c>
       <c r="F8"/>
@@ -2346,7 +2423,7 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B9" t="s">
@@ -2358,7 +2435,7 @@
       <c r="D9" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F9"/>
@@ -2367,7 +2444,7 @@
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B10" t="s">
@@ -2379,7 +2456,7 @@
       <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="8" t="s">
         <v>49</v>
       </c>
       <c r="F10"/>
@@ -2388,7 +2465,7 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B11" t="s">
@@ -2400,7 +2477,7 @@
       <c r="D11" t="s">
         <v>54</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="8" t="s">
         <v>55</v>
       </c>
       <c r="F11"/>
@@ -2409,7 +2486,7 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>57</v>
       </c>
       <c r="B12" t="s">
@@ -2421,7 +2498,7 @@
       <c r="D12" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="8" t="s">
         <v>60</v>
       </c>
       <c r="F12"/>
@@ -2430,7 +2507,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:8">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>62</v>
       </c>
       <c r="B13" t="s">
@@ -2442,7 +2519,7 @@
       <c r="D13" t="s">
         <v>63</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F13"/>
@@ -2451,7 +2528,7 @@
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>66</v>
       </c>
       <c r="B14" t="s">
@@ -2463,7 +2540,7 @@
       <c r="D14" t="s">
         <v>69</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="8" t="s">
         <v>70</v>
       </c>
       <c r="F14"/>
@@ -2472,7 +2549,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:8">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>72</v>
       </c>
       <c r="B15" t="s">
@@ -2484,7 +2561,7 @@
       <c r="D15" t="s">
         <v>75</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="8" t="s">
         <v>76</v>
       </c>
       <c r="F15"/>
@@ -2493,7 +2570,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:8">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B16" t="s">
@@ -2502,7 +2579,7 @@
       <c r="D16" t="s">
         <v>80</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F16"/>
@@ -2511,13 +2588,13 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:7">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>83</v>
       </c>
       <c r="B17" t="s">
         <v>84</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="8" t="s">
         <v>85</v>
       </c>
       <c r="F17"/>
@@ -2526,13 +2603,13 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:7">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>88</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="8" t="s">
         <v>89</v>
       </c>
       <c r="F18"/>
@@ -2541,13 +2618,13 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:7">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>92</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F19"/>
@@ -2556,13 +2633,13 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:7">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>94</v>
       </c>
       <c r="B20" t="s">
         <v>95</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="8" t="s">
         <v>96</v>
       </c>
       <c r="F20"/>
@@ -2571,13 +2648,13 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B21" t="s">
         <v>98</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="8" t="s">
         <v>99</v>
       </c>
       <c r="F21"/>
@@ -2586,7 +2663,7 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>100</v>
       </c>
       <c r="B22" t="s">
@@ -2595,7 +2672,7 @@
       <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="8" t="s">
         <v>103</v>
       </c>
       <c r="F22"/>
@@ -2604,7 +2681,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:7">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>105</v>
       </c>
       <c r="B23" t="s">
@@ -2613,7 +2690,7 @@
       <c r="D23" t="s">
         <v>106</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="8" t="s">
         <v>107</v>
       </c>
       <c r="F23"/>
@@ -2622,7 +2699,7 @@
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>108</v>
       </c>
       <c r="B24" t="s">
@@ -2631,7 +2708,7 @@
       <c r="D24" t="s">
         <v>110</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="8" t="s">
         <v>111</v>
       </c>
       <c r="F24"/>
@@ -2640,13 +2717,13 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:7">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="8" t="s">
         <v>113</v>
       </c>
       <c r="F25"/>
@@ -2655,7 +2732,7 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:7">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>114</v>
       </c>
       <c r="B26" t="s">
@@ -2664,7 +2741,7 @@
       <c r="D26" t="s">
         <v>116</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="8" t="s">
         <v>117</v>
       </c>
       <c r="F26"/>
@@ -2673,7 +2750,7 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:7">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>118</v>
       </c>
       <c r="B27" t="s">
@@ -2682,7 +2759,7 @@
       <c r="D27" t="s">
         <v>120</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="8" t="s">
         <v>121</v>
       </c>
       <c r="F27"/>
@@ -2691,13 +2768,13 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:7">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>123</v>
       </c>
       <c r="B28" t="s">
         <v>124</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="8" t="s">
         <v>125</v>
       </c>
       <c r="F28"/>
@@ -2706,13 +2783,13 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:7">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>126</v>
       </c>
       <c r="B29" t="s">
         <v>127</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="8" t="s">
         <v>128</v>
       </c>
       <c r="F29"/>
@@ -2721,7 +2798,7 @@
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:7">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B30" t="s">
@@ -2730,7 +2807,7 @@
       <c r="D30" t="s">
         <v>132</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="8" t="s">
         <v>133</v>
       </c>
       <c r="F30"/>
@@ -2739,13 +2816,13 @@
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:7">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>135</v>
       </c>
       <c r="B31" t="s">
         <v>136</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="8" t="s">
         <v>137</v>
       </c>
       <c r="F31"/>
@@ -2754,13 +2831,13 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:7">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="7" t="s">
         <v>139</v>
       </c>
       <c r="B32" t="s">
         <v>140</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="8" t="s">
         <v>141</v>
       </c>
       <c r="F32"/>
@@ -2769,13 +2846,13 @@
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:7">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>142</v>
       </c>
       <c r="B33" t="s">
         <v>143</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="8" t="s">
         <v>144</v>
       </c>
       <c r="F33"/>
@@ -2784,13 +2861,13 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:7">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="7" t="s">
         <v>146</v>
       </c>
       <c r="B34" t="s">
         <v>147</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="8" t="s">
         <v>148</v>
       </c>
       <c r="F34"/>
@@ -2799,13 +2876,13 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:7">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>149</v>
       </c>
       <c r="B35" t="s">
         <v>150</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="8" t="s">
         <v>151</v>
       </c>
       <c r="F35"/>
@@ -2814,7 +2891,7 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:7">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="7" t="s">
         <v>152</v>
       </c>
       <c r="B36" t="s">
@@ -2823,7 +2900,7 @@
       <c r="D36" t="s">
         <v>154</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="8" t="s">
         <v>155</v>
       </c>
       <c r="F36"/>
@@ -2832,7 +2909,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:7">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="7" t="s">
         <v>157</v>
       </c>
       <c r="B37" t="s">
@@ -2841,7 +2918,7 @@
       <c r="D37" t="s">
         <v>159</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="8" t="s">
         <v>160</v>
       </c>
       <c r="F37"/>
@@ -2850,7 +2927,7 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:7">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>162</v>
       </c>
       <c r="B38" t="s">
@@ -2859,7 +2936,7 @@
       <c r="D38" t="s">
         <v>164</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="8" t="s">
         <v>165</v>
       </c>
       <c r="F38"/>
@@ -2868,7 +2945,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:7">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="7" t="s">
         <v>166</v>
       </c>
       <c r="B39" t="s">
@@ -2877,7 +2954,7 @@
       <c r="D39" t="s">
         <v>168</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="8" t="s">
         <v>169</v>
       </c>
       <c r="F39"/>
@@ -2886,7 +2963,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:7">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>171</v>
       </c>
       <c r="B40" t="s">
@@ -2895,7 +2972,7 @@
       <c r="D40" t="s">
         <v>173</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="8" t="s">
         <v>174</v>
       </c>
       <c r="F40"/>
@@ -2904,7 +2981,7 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:7">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="7" t="s">
         <v>175</v>
       </c>
       <c r="B41" t="s">
@@ -2913,7 +2990,7 @@
       <c r="D41" t="s">
         <v>177</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="8" t="s">
         <v>178</v>
       </c>
       <c r="F41"/>
@@ -2922,13 +2999,13 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:7">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>179</v>
       </c>
       <c r="B42" t="s">
         <v>180</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="8" t="s">
         <v>181</v>
       </c>
       <c r="F42"/>
@@ -2937,13 +3014,13 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:7">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>183</v>
       </c>
       <c r="B43" t="s">
         <v>184</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="8" t="s">
         <v>185</v>
       </c>
       <c r="F43"/>
@@ -2952,7 +3029,7 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:7">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>186</v>
       </c>
       <c r="B44" t="s">
@@ -2961,7 +3038,7 @@
       <c r="D44" t="s">
         <v>188</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="8" t="s">
         <v>189</v>
       </c>
       <c r="F44"/>
@@ -2970,7 +3047,7 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:7">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>191</v>
       </c>
       <c r="B45" t="s">
@@ -2979,7 +3056,7 @@
       <c r="D45" t="s">
         <v>192</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="8" t="s">
         <v>193</v>
       </c>
       <c r="F45"/>
@@ -2988,13 +3065,13 @@
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:7">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>194</v>
       </c>
       <c r="B46" t="s">
         <v>195</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="8" t="s">
         <v>196</v>
       </c>
       <c r="F46"/>
@@ -3003,13 +3080,13 @@
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:7">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="7" t="s">
         <v>198</v>
       </c>
       <c r="B47" t="s">
         <v>199</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="8" t="s">
         <v>200</v>
       </c>
       <c r="F47"/>
@@ -3018,7 +3095,7 @@
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:7">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>201</v>
       </c>
       <c r="B48" t="s">
@@ -3027,7 +3104,7 @@
       <c r="D48" t="s">
         <v>203</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="8" t="s">
         <v>204</v>
       </c>
       <c r="F48"/>
@@ -3036,7 +3113,7 @@
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:7">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="7" t="s">
         <v>205</v>
       </c>
       <c r="B49" t="s">
@@ -3045,7 +3122,7 @@
       <c r="D49" t="s">
         <v>207</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="8" t="s">
         <v>208</v>
       </c>
       <c r="F49"/>
@@ -3054,7 +3131,7 @@
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:7">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>210</v>
       </c>
       <c r="B50" t="s">
@@ -3063,7 +3140,7 @@
       <c r="D50" t="s">
         <v>212</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F50"/>
@@ -3072,13 +3149,13 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:7">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="7" t="s">
         <v>215</v>
       </c>
       <c r="B51" t="s">
         <v>216</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="8" t="s">
         <v>217</v>
       </c>
       <c r="F51"/>
@@ -3087,13 +3164,13 @@
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:7">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>219</v>
       </c>
       <c r="B52" t="s">
         <v>220</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F52"/>
@@ -3102,13 +3179,13 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:7">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>222</v>
       </c>
       <c r="B53" t="s">
         <v>223</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="8" t="s">
         <v>224</v>
       </c>
       <c r="F53"/>
@@ -3117,13 +3194,13 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:7">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>225</v>
       </c>
       <c r="B54" t="s">
         <v>226</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="8" t="s">
         <v>227</v>
       </c>
       <c r="F54"/>
@@ -3132,13 +3209,13 @@
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:7">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="7" t="s">
         <v>228</v>
       </c>
       <c r="B55" t="s">
         <v>226</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="8" t="s">
         <v>229</v>
       </c>
       <c r="F55"/>
@@ -3147,7 +3224,7 @@
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:7">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>230</v>
       </c>
       <c r="B56" t="s">
@@ -3156,7 +3233,7 @@
       <c r="D56" t="s">
         <v>232</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="8" t="s">
         <v>233</v>
       </c>
       <c r="F56"/>
@@ -3165,7 +3242,7 @@
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:7">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="7" t="s">
         <v>235</v>
       </c>
       <c r="B57" t="s">
@@ -3174,7 +3251,7 @@
       <c r="D57" t="s">
         <v>237</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="8" t="s">
         <v>238</v>
       </c>
       <c r="F57"/>
@@ -3183,13 +3260,13 @@
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:7">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>240</v>
       </c>
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="8" t="s">
         <v>242</v>
       </c>
       <c r="F58"/>
@@ -3198,13 +3275,13 @@
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:7">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="7" t="s">
         <v>243</v>
       </c>
       <c r="B59" t="s">
         <v>244</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="8" t="s">
         <v>245</v>
       </c>
       <c r="F59"/>
@@ -3213,13 +3290,13 @@
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:7">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="7" t="s">
         <v>246</v>
       </c>
       <c r="B60" t="s">
         <v>247</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="8" t="s">
         <v>248</v>
       </c>
       <c r="F60"/>
@@ -3228,13 +3305,13 @@
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:7">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="7" t="s">
         <v>249</v>
       </c>
       <c r="B61" t="s">
         <v>250</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="8" t="s">
         <v>251</v>
       </c>
       <c r="F61"/>
@@ -3243,7 +3320,7 @@
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:7">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="7" t="s">
         <v>252</v>
       </c>
       <c r="B62" t="s">
@@ -3252,7 +3329,7 @@
       <c r="D62" t="s">
         <v>254</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="8" t="s">
         <v>255</v>
       </c>
       <c r="F62"/>
@@ -3261,13 +3338,13 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:7">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="7" t="s">
         <v>256</v>
       </c>
       <c r="B63" t="s">
         <v>257</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="8" t="s">
         <v>258</v>
       </c>
       <c r="F63"/>
@@ -3276,18 +3353,35 @@
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:7">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="7" t="s">
         <v>260</v>
       </c>
       <c r="B64" t="s">
         <v>261</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="8" t="s">
         <v>262</v>
       </c>
       <c r="F64"/>
       <c r="G64" t="s">
         <v>263</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:5">
+      <c r="A65" s="9">
+        <v>8415200000</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
